--- a/output/2026-09-01_18_Italia_Umbria_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-01_18_Italia_Umbria_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -498,10 +498,9 @@
           <t>075 5996452</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore di ferramenta industriale e forniture tecniche dal 2004 (bulloneria, utensili manuali/elettrici, DPI, abrasivi, sollevamento). Anche rivenditore STIGA (giardinaggio, attività accessoria).</t>
+          <t>Distributore di ferramenta industriale e forniture tecniche dal 2004 (bulloneria, utensili manuali/elettrici, DPI, abrasivi, sollevamento). Anche rivenditore STIGA (giardinaggio, attività accessoria). [DUPLICATO — vedi anche: 2026-09-01_15_Italia_Umbria_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +535,6 @@
           <t>075 5179441</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Distributore di metalli ferrosi e non ferrosi, alluminio, rame, acciaio inox, materiali plastici, scaffalature industriali.</t>
@@ -574,10 +572,9 @@
           <t>075 5173731 / 328 3420573</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vendita, assistenza e riparazione utensileria e macchine utensili; distributore ufficiale Facom (Master Facom Club), Zeca, Ecotechnics.</t>
+          <t>Vendita, assistenza e riparazione utensileria e macchine utensili; distributore ufficiale Facom (Master Facom Club), Zeca, Ecotechnics. [DUPLICATO — vedi anche: 2026-09-01_15_Italia_Umbria_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,7 +609,6 @@
           <t>075 9724062</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Commercio macchine utensili nuove/usate (torni CNC, fresatrici CNC, centri di lavoro, presse piegatrici), brand 'Macchine Utensili by Liberti', operativo da oltre 40 anni.</t>
@@ -650,10 +646,9 @@
           <t>075 3766637</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rivenditore macchine utensili per lavorazione metalli nuove/usate (cesoie, presse piegatrici, seghe a nastro, torni, fresatrici, rettificatrici, trapani).</t>
+          <t>Rivenditore macchine utensili per lavorazione metalli nuove/usate (cesoie, presse piegatrici, seghe a nastro, torni, fresatrici, rettificatrici, trapani). [DUPLICATO — vedi anche: 2026-09-01_15_Italia_Umbria_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -688,10 +683,9 @@
           <t>0744 814812 / 0744 815960</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Forniture industriali (trasmissioni, idraulica, pneumatica), cuscinetti e utensileria per settore industriale/artigianale, fondata 2006.</t>
+          <t>Forniture industriali (trasmissioni, idraulica, pneumatica), cuscinetti e utensileria per settore industriale/artigianale, fondata 2006. [DUPLICATO — vedi anche: 2026-09-01_05_Italia_Umbria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,7 +700,6 @@
           <t>Tecnol S.r.l.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Terni (TR)</t>
@@ -722,7 +715,6 @@
           <t>0744 424641</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Forniture industriali a Terni; verificato solo tramite elenchi di settore (PagineGialle/PagineBianche/ReteImprese), nessun sito ufficiale reperito, dati limitati.</t>
@@ -755,11 +747,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Commercio all'ingrosso di ferramenta (ATECO 46.84.10). Sede legale risulta Via Pistoia 3, Ferentillo (indirizzo non pienamente confermato rispetto a quello grezzo).</t>
+          <t>Commercio all'ingrosso di ferramenta (ATECO 46.84.10). Sede legale risulta Via Pistoia 3, Ferentillo (indirizzo non pienamente confermato rispetto a quello grezzo). [DUPLICATO — vedi anche: 2026-09-01_15_Italia_Umbria_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -801,7 +791,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ferramenta industriale ingrosso/dettaglio, utensileria professionale, elettroutensili, saldatura, DPI, accessori alluminio/ferro.</t>
+          <t>Ferramenta industriale ingrosso/dettaglio, utensileria professionale, elettroutensili, saldatura, DPI, accessori alluminio/ferro. [DUPLICATO — vedi anche: 2026-09-01_15_Italia_Umbria_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -878,7 +868,6 @@
           <t>075 8472313</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Distributore ferramenta, compressori, raccorderia pneumatica, elettromeccanica dal 1985. Attività mista, include anche giardinaggio (dealer Honda/STIGA).</t>
